--- a/docs/SJ2024.xlsx
+++ b/docs/SJ2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edilbertosuarez/Documents/Proyectos/icfes/icfes-analyzer/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CF35CB-61E5-7E4A-9BCA-0E5124D2349C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED5E7E5-A41D-9641-807E-AAB61E3EFFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
+    <workbookView xWindow="4460" yWindow="500" windowWidth="21140" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="163">
   <si>
     <t>Grupo</t>
   </si>
@@ -74,15 +74,6 @@
     <t>Apellido</t>
   </si>
   <si>
-    <t>Percentil Lectura crítica</t>
-  </si>
-  <si>
-    <t>Percentil Matemáticas</t>
-  </si>
-  <si>
-    <t>Percentil Sociales</t>
-  </si>
-  <si>
     <t>MARIANA</t>
   </si>
   <si>
@@ -135,21 +126,6 @@
   </si>
   <si>
     <t>11°3</t>
-  </si>
-  <si>
-    <t>Percentil Naturales</t>
-  </si>
-  <si>
-    <t>Percentil Inglés</t>
-  </si>
-  <si>
-    <t>Competencia</t>
-  </si>
-  <si>
-    <t>Componente</t>
-  </si>
-  <si>
-    <t>% Acierto</t>
   </si>
   <si>
     <t>ALVAREZ CASTRO</t>
@@ -934,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8049E5-A74E-1849-8EE1-5BE190AEA293}">
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.5" customWidth="1"/>
@@ -942,7 +918,7 @@
     <col min="12" max="12" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,43 +949,19 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
       </c>
       <c r="E2">
         <v>55</v>
@@ -1030,18 +982,18 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E3">
         <v>57</v>
@@ -1062,18 +1014,18 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E4">
         <v>66</v>
@@ -1094,18 +1046,18 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E5">
         <v>62</v>
@@ -1126,18 +1078,18 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E6">
         <v>66</v>
@@ -1158,18 +1110,18 @@
         <v>331</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>51</v>
@@ -1190,18 +1142,18 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>45</v>
@@ -1222,18 +1174,18 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>67</v>
@@ -1254,18 +1206,18 @@
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E10">
         <v>66</v>
@@ -1286,18 +1238,18 @@
         <v>342</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E11">
         <v>60</v>
@@ -1318,18 +1270,18 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E12">
         <v>73</v>
@@ -1350,18 +1302,18 @@
         <v>343</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E13">
         <v>66</v>
@@ -1382,18 +1334,18 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14">
         <v>62</v>
@@ -1414,18 +1366,18 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E15">
         <v>75</v>
@@ -1446,18 +1398,18 @@
         <v>345</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>59</v>
@@ -1483,13 +1435,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>65</v>
@@ -1515,13 +1467,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>68</v>
@@ -1547,13 +1499,13 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E19">
         <v>66</v>
@@ -1579,13 +1531,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E20">
         <v>63</v>
@@ -1611,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E21">
         <v>75</v>
@@ -1643,13 +1595,13 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E22">
         <v>61</v>
@@ -1675,13 +1627,13 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E23">
         <v>67</v>
@@ -1707,13 +1659,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E24">
         <v>58</v>
@@ -1739,13 +1691,13 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E25">
         <v>58</v>
@@ -1771,13 +1723,13 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>64</v>
@@ -1803,13 +1755,13 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E27">
         <v>71</v>
@@ -1835,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>63</v>
@@ -1867,13 +1819,13 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E29">
         <v>63</v>
@@ -1899,13 +1851,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E30">
         <v>46</v>
@@ -1931,13 +1883,13 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E31">
         <v>65</v>
@@ -1963,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E32">
         <v>74</v>
@@ -1995,13 +1947,13 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E33">
         <v>67</v>
@@ -2027,13 +1979,13 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
         <v>84</v>
-      </c>
-      <c r="D34" t="s">
-        <v>92</v>
       </c>
       <c r="E34">
         <v>69</v>
@@ -2059,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" t="s">
         <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>93</v>
       </c>
       <c r="E35">
         <v>60</v>
@@ -2091,13 +2043,13 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E36">
         <v>69</v>
@@ -2123,13 +2075,13 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>71</v>
@@ -2155,13 +2107,13 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E38">
         <v>69</v>
@@ -2187,13 +2139,13 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E39">
         <v>54</v>
@@ -2219,13 +2171,13 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>100</v>
@@ -2251,13 +2203,13 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>76</v>
@@ -2283,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E42">
         <v>51</v>
@@ -2315,13 +2267,13 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E43">
         <v>56</v>
@@ -2347,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E44">
         <v>75</v>
@@ -2379,13 +2331,13 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E45">
         <v>63</v>
@@ -2411,13 +2363,13 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E46">
         <v>55</v>
@@ -2443,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E47">
         <v>62</v>
@@ -2475,13 +2427,13 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E48">
         <v>65</v>
@@ -2507,13 +2459,13 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E49">
         <v>68</v>
@@ -2539,13 +2491,13 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <v>53</v>
@@ -2571,13 +2523,13 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E51">
         <v>56</v>
@@ -2603,13 +2555,13 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>65</v>
@@ -2635,13 +2587,13 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E53">
         <v>54</v>
@@ -2667,13 +2619,13 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2699,13 +2651,13 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E55">
         <v>68</v>
@@ -2731,13 +2683,13 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E56">
         <v>56</v>
@@ -2763,13 +2715,13 @@
         <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E57">
         <v>59</v>
@@ -2795,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E58">
         <v>69</v>
@@ -2827,13 +2779,13 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E59">
         <v>57</v>
@@ -2859,13 +2811,13 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E60">
         <v>63</v>
@@ -2891,13 +2843,13 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E61">
         <v>66</v>
@@ -2923,13 +2875,13 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D62" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E62">
         <v>70</v>
@@ -2955,13 +2907,13 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E63">
         <v>65</v>
@@ -2987,13 +2939,13 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -3019,13 +2971,13 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E65">
         <v>54</v>
@@ -3051,13 +3003,13 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E66">
         <v>63</v>
@@ -3083,13 +3035,13 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E67">
         <v>69</v>
@@ -3115,13 +3067,13 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E68">
         <v>57</v>
@@ -3147,13 +3099,13 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E69">
         <v>58</v>
@@ -3179,13 +3131,13 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E70">
         <v>57</v>
@@ -3211,13 +3163,13 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E71">
         <v>62</v>
@@ -3243,13 +3195,13 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E72">
         <v>44</v>
@@ -3275,13 +3227,13 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E73">
         <v>51</v>
@@ -3307,13 +3259,13 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D74" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E74">
         <v>62</v>
@@ -3339,13 +3291,13 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E75">
         <v>66</v>
@@ -3371,13 +3323,13 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E76">
         <v>57</v>
@@ -3403,13 +3355,13 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E77">
         <v>54</v>
@@ -3435,13 +3387,13 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E78">
         <v>81</v>
@@ -3467,13 +3419,13 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C79" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D79" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E79">
         <v>40</v>
@@ -3499,13 +3451,13 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E80">
         <v>56</v>
@@ -3531,13 +3483,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C81" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E81">
         <v>69</v>
@@ -3563,13 +3515,13 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C82" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D82" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E82">
         <v>62</v>
@@ -3595,13 +3547,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C83" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D83" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E83">
         <v>55</v>
@@ -3627,13 +3579,13 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E84">
         <v>57</v>
@@ -3659,13 +3611,13 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E85">
         <v>65</v>
@@ -3691,13 +3643,13 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D86" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E86">
         <v>71</v>
@@ -3723,13 +3675,13 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C87" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D87" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E87">
         <v>65</v>
@@ -3755,13 +3707,13 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C88" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D88" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E88">
         <v>71</v>
@@ -3787,13 +3739,13 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C89" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E89">
         <v>66</v>
@@ -3819,13 +3771,13 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D90" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E90">
         <v>63</v>
@@ -3851,13 +3803,13 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C91" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D91" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E91">
         <v>59</v>
@@ -3883,13 +3835,13 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E92">
         <v>66</v>
@@ -3915,13 +3867,13 @@
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C93" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D93" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E93">
         <v>68</v>
@@ -3947,13 +3899,13 @@
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E94">
         <v>73</v>
@@ -3979,13 +3931,13 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D95" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E95">
         <v>71</v>
@@ -4011,13 +3963,13 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E96">
         <v>61</v>
@@ -4043,13 +3995,13 @@
         <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C97" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E97">
         <v>54</v>
@@ -4075,13 +4027,13 @@
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E98">
         <v>68</v>

--- a/docs/SJ2024.xlsx
+++ b/docs/SJ2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edilbertosuarez/Documents/Proyectos/icfes/icfes-analyzer/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED5E7E5-A41D-9641-807E-AAB61E3EFFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962DFC25-136C-A149-B292-71AF186DC773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4460" yWindow="500" windowWidth="21140" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="173">
   <si>
     <t>Grupo</t>
   </si>
@@ -525,6 +525,36 @@
   </si>
   <si>
     <t>VELEZ RAMIREZ</t>
+  </si>
+  <si>
+    <t>% LC</t>
+  </si>
+  <si>
+    <t>% MAT</t>
+  </si>
+  <si>
+    <t>% SOC</t>
+  </si>
+  <si>
+    <t>% NAT</t>
+  </si>
+  <si>
+    <t>% ING</t>
+  </si>
+  <si>
+    <t>Nivel LC</t>
+  </si>
+  <si>
+    <t>Nivel MAT</t>
+  </si>
+  <si>
+    <t>Nivel SOC</t>
+  </si>
+  <si>
+    <t>Nivel NAT</t>
+  </si>
+  <si>
+    <t>Nivel ING</t>
   </si>
 </sst>
 </file>
@@ -910,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8049E5-A74E-1849-8EE1-5BE190AEA293}">
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:T98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.5" customWidth="1"/>
@@ -918,7 +948,7 @@
     <col min="12" max="12" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -949,8 +979,38 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1" t="s">
+        <v>164</v>
+      </c>
+      <c r="M1" t="s">
+        <v>165</v>
+      </c>
+      <c r="N1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O1" t="s">
+        <v>167</v>
+      </c>
+      <c r="P1" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>169</v>
+      </c>
+      <c r="R1" t="s">
+        <v>170</v>
+      </c>
+      <c r="S1" t="s">
+        <v>171</v>
+      </c>
+      <c r="T1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -982,7 +1042,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1014,7 +1074,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1046,7 +1106,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1078,7 +1138,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1170,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1142,7 +1202,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1174,7 +1234,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1206,7 +1266,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1238,7 +1298,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1270,7 +1330,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1302,7 +1362,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1334,7 +1394,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1366,7 +1426,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1398,7 +1458,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
